--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.107.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.107.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.107" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.107" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.107.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0107.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0107.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.107.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.107.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.107" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.107" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -595,20 +595,32 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]100</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]100</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 100</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]100</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
@@ -633,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -642,12 +654,12 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Committee, terâ€™s office a proposal for such appointment and for the</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L173: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -718,12 +730,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -824,7 +836,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L64: symbol-only separator/garbage line :: (190).</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -867,7 +879,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 100</t>
+          <t>L64: symbol-only separator/garbage line :: (190).</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -910,7 +922,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L84: symbol-only separator/garbage line :: (48).</t>
+          <t>L70: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -933,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -953,7 +965,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L116: symbol-only separator/garbage line :: (188).</t>
+          <t>L84: symbol-only separator/garbage line :: (48).</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -981,7 +993,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -996,7 +1008,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L152: symbol-only separator/garbage line :: (189).</t>
+          <t>L116: symbol-only separator/garbage line :: (188).</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1019,12 +1031,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1039,7 +1051,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L168: isolated marker/symbol line :: S</t>
+          <t>L152: symbol-only separator/garbage line :: (189).</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1082,7 +1094,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L175: symbol-only separator/garbage line :: (190).</t>
+          <t>L168: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1125,7 +1137,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: A</t>
+          <t>L173: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1168,7 +1180,7 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L187: isolated marker/symbol line :: A</t>
+          <t>L175: symbol-only separator/garbage line :: (190).</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr"/>
@@ -1209,7 +1221,11 @@
       <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>L186: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O16" s="1" t="inlineStr"/>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
@@ -1248,7 +1264,11 @@
       <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
-      <c r="N17" s="1" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>L187: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O17" s="1" t="inlineStr"/>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
